--- a/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:35:17+00:00</t>
+    <t>2024-04-03T14:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
